--- a/مدیریت داده ها-جدید.xlsx
+++ b/مدیریت داده ها-جدید.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ZBook\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CD06117-5D12-4335-A17D-C1304ADF588A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2522A97C-0480-4FA9-9308-0F8DC709E6FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{C15FB9D3-F47A-4155-8B69-7DA654384DF7}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{C15FB9D3-F47A-4155-8B69-7DA654384DF7}"/>
   </bookViews>
   <sheets>
     <sheet name="مدیریت داده" sheetId="1" r:id="rId1"/>
     <sheet name="قیمت تمام شده" sheetId="2" r:id="rId2"/>
     <sheet name="حق الزحمه" sheetId="3" r:id="rId3"/>
+    <sheet name="فاکتور فروش" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="56">
   <si>
     <t>ردیف</t>
   </si>
@@ -167,6 +168,45 @@
   </si>
   <si>
     <t>تهمینه دماوندی</t>
+  </si>
+  <si>
+    <t>فاکتور فروش</t>
+  </si>
+  <si>
+    <t>نام کالا</t>
+  </si>
+  <si>
+    <t>تعداد</t>
+  </si>
+  <si>
+    <t>قیمت واحد</t>
+  </si>
+  <si>
+    <t>قیمت کل</t>
+  </si>
+  <si>
+    <t>ماگ فانتزی</t>
+  </si>
+  <si>
+    <t>گل سر زرین چفتی</t>
+  </si>
+  <si>
+    <t>جمع کل</t>
+  </si>
+  <si>
+    <t>درصد تخفیف</t>
+  </si>
+  <si>
+    <t>مبلغ قابل پرداخت</t>
+  </si>
+  <si>
+    <t>نام مشتری</t>
+  </si>
+  <si>
+    <t>شماره فاکتور</t>
+  </si>
+  <si>
+    <t>تاریخ</t>
   </si>
 </sst>
 </file>
@@ -179,7 +219,7 @@
     <numFmt numFmtId="166" formatCode="_ * #,##0_-[$ريال-429]_ ;_ * #,##0\-[$ريال-429]_ ;_ * &quot;-&quot;_-[$ريال-429]_ ;_ @_ "/>
     <numFmt numFmtId="167" formatCode="#,##0.00_-[$ريال-429]"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -219,8 +259,20 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="2  Mitra"/>
+      <charset val="178"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="2  Mitra"/>
+      <charset val="178"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -251,6 +303,24 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF9933"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC66"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF66FFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -376,7 +446,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -405,6 +475,24 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -690,6 +778,11 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF66FFFF"/>
+      <color rgb="FFFFCC66"/>
+      <color rgb="FFFF9933"/>
+      <color rgb="FFFF7C80"/>
+      <color rgb="FFFF9900"/>
       <color rgb="FF339966"/>
       <color rgb="FF33CC33"/>
       <color rgb="FFCCFFCC"/>
@@ -1608,4 +1701,201 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{020CA6FE-FDC0-4911-B021-A32E628E9BBA}">
+  <dimension ref="A1:H14"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="5.1796875" customWidth="1"/>
+    <col min="2" max="2" width="15.26953125" customWidth="1"/>
+    <col min="3" max="3" width="4.81640625" customWidth="1"/>
+    <col min="7" max="7" width="9.36328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="G1" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="H1" s="26"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="D2" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="E2" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="G2" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="H2" s="29"/>
+    </row>
+    <row r="3" spans="1:8" ht="16.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="28">
+        <v>1</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="28">
+        <v>2</v>
+      </c>
+      <c r="D3" s="30">
+        <v>110000</v>
+      </c>
+      <c r="E3" s="31">
+        <f>C3*D3</f>
+        <v>220000</v>
+      </c>
+      <c r="G3" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="H3" s="29"/>
+    </row>
+    <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="28">
+        <v>2</v>
+      </c>
+      <c r="B4" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="28">
+        <v>1</v>
+      </c>
+      <c r="D4" s="30">
+        <v>200000</v>
+      </c>
+      <c r="E4" s="31">
+        <f>C4*D4</f>
+        <v>200000</v>
+      </c>
+      <c r="G4" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="H4" s="29"/>
+    </row>
+    <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="28">
+        <v>3</v>
+      </c>
+      <c r="B5" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" s="28">
+        <v>1</v>
+      </c>
+      <c r="D5" s="30">
+        <v>70000</v>
+      </c>
+      <c r="E5" s="31">
+        <f>C5*D5</f>
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" s="29"/>
+      <c r="B6" s="29"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="29"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" s="29"/>
+      <c r="B7" s="29"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="29"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" s="29"/>
+      <c r="B8" s="29"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" s="29"/>
+      <c r="B9" s="29"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" s="29"/>
+      <c r="B10" s="29"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="29"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" s="29"/>
+      <c r="B11" s="29"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+    </row>
+    <row r="12" spans="1:8" ht="16.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" s="32"/>
+      <c r="C12" s="32"/>
+      <c r="D12" s="32"/>
+      <c r="E12" s="30">
+        <f>SUM(E3:E5)</f>
+        <v>490000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="16" x14ac:dyDescent="0.5">
+      <c r="A13" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13" s="32"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="32"/>
+      <c r="E13" s="33" t="str">
+        <f>IF(C15 &gt; 2000000, "10 %", "5 %")</f>
+        <v>5 %</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="16.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="32" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" s="32"/>
+      <c r="C14" s="32"/>
+      <c r="D14" s="32"/>
+      <c r="E14" s="30">
+        <f>IF(E12 &gt; 200000, E12 - (E12 * 10/100), E12 - (E12 * 5/100))</f>
+        <v>441000</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A14:D14"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>